--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -1163,7 +1163,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B5" s="17">
         <f>COUNTIF('Kernel Track'!F2:F27,"Done")</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>27</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B7" s="18">
         <f>B5/B6</f>
-        <v>0.5384615385</v>
+        <v>0.6538461538</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>186</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.25</v>
+        <v>0.3035714286</v>
       </c>
     </row>
     <row r="14">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B19" s="17">
         <f>COUNTIFS('Kernel Track'!A2:A1000,"Month 4 - Server &amp; security core",'Kernel Track'!F2:F1000,"Done")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" s="17">
         <f>COUNTIF('Kernel Track'!A2:A1000,"Month 4 - Server &amp; security core")</f>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="D19" s="24">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2588,12 +2588,12 @@
   <printOptions/>
   <pageMargins bottom="0.5" footer="0.0" header="0.0" left="0.4" right="0.4" top="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <drawing ns1:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2942,8 +2942,8 @@
       <c r="E16" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>26</v>
+      <c r="F16" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="G16" s="13"/>
     </row>
@@ -2963,8 +2963,8 @@
       <c r="E17" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>26</v>
+      <c r="F17" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="G17" s="13"/>
     </row>
@@ -2984,8 +2984,8 @@
       <c r="E18" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>26</v>
+      <c r="F18" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="G18" s="13"/>
     </row>
@@ -4170,7 +4170,7 @@
   <printOptions/>
   <pageMargins bottom="0.5" footer="0.0" header="0.0" left="0.35" right="0.35" top="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <drawing ns1:id="rId1"/>
 </worksheet>
 </file>
 

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B5" s="17">
         <f>COUNTIF('Kernel Track'!F2:F27,"Done")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>27</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B7" s="18">
         <f>B5/B6</f>
-        <v>0.6538461538</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>186</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.3035714286</v>
+        <v>0.32142857142857145</v>
       </c>
     </row>
     <row r="14">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B20" s="17">
         <f>COUNTIFS('Kernel Track'!A2:A1000,"Month 5 - Driver breadth &amp; performance",'Kernel Track'!F2:F1000,"Done")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" s="17">
         <f>COUNTIF('Kernel Track'!A2:A1000,"Month 5 - Driver breadth &amp; performance")</f>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="D20" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -3002,11 +3002,11 @@
       <c r="D19" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="11" t="s">
-        <v>26</v>
+      <c r="F19" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="G19" s="13"/>
     </row>

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -1163,7 +1163,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B5" s="17">
         <f>COUNTIF('Kernel Track'!F2:F27,"Done")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>27</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B7" s="18">
         <f>B5/B6</f>
-        <v>0.6923076923076923</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>186</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.32142857142857145</v>
+        <v>0.3392857142857143</v>
       </c>
     </row>
     <row r="14">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B20" s="17">
         <f>COUNTIFS('Kernel Track'!A2:A1000,"Month 5 - Driver breadth &amp; performance",'Kernel Track'!F2:F1000,"Done")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="17">
         <f>COUNTIF('Kernel Track'!A2:A1000,"Month 5 - Driver breadth &amp; performance")</f>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="D20" s="24">
         <f t="shared" si="2"/>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -2588,12 +2588,12 @@
   <printOptions/>
   <pageMargins bottom="0.5" footer="0.0" header="0.0" left="0.4" right="0.4" top="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
-  <drawing ns1:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3023,11 +3023,11 @@
       <c r="D20" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>26</v>
+      <c r="F20" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="G20" s="13"/>
     </row>
@@ -4170,7 +4170,7 @@
   <printOptions/>
   <pageMargins bottom="0.5" footer="0.0" header="0.0" left="0.35" right="0.35" top="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
-  <drawing ns1:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B5" s="17">
         <f>COUNTIF('Kernel Track'!F2:F27,"Done")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>27</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B7" s="18">
         <f>B5/B6</f>
-        <v>0.7307692307692307</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>186</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.3392857142857143</v>
+        <v>0.35714285714285715</v>
       </c>
     </row>
     <row r="14">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B20" s="17">
         <f>COUNTIFS('Kernel Track'!A2:A1000,"Month 5 - Driver breadth &amp; performance",'Kernel Track'!F2:F1000,"Done")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" s="17">
         <f>COUNTIF('Kernel Track'!A2:A1000,"Month 5 - Driver breadth &amp; performance")</f>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="D20" s="24">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -3044,11 +3044,11 @@
       <c r="D21" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="11" t="s">
-        <v>26</v>
+      <c r="F21" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="G21" s="13"/>
     </row>

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -1163,7 +1163,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B5" s="17">
         <f>COUNTIF('Kernel Track'!F2:F27,"Done")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>27</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B7" s="18">
         <f>B5/B6</f>
-        <v>0.7692307692307693</v>
+        <v>0.8076923076923077</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>186</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.35714285714285715</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="14">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B20" s="17">
         <f>COUNTIFS('Kernel Track'!A2:A1000,"Month 5 - Driver breadth &amp; performance",'Kernel Track'!F2:F1000,"Done")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" s="17">
         <f>COUNTIF('Kernel Track'!A2:A1000,"Month 5 - Driver breadth &amp; performance")</f>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="D20" s="24">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -2588,12 +2588,12 @@
   <printOptions/>
   <pageMargins bottom="0.5" footer="0.0" header="0.0" left="0.4" right="0.4" top="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <drawing ns1:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3068,8 +3068,8 @@
       <c r="E22" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="11" t="s">
-        <v>26</v>
+      <c r="F22" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="G22" s="13"/>
     </row>
@@ -4170,7 +4170,7 @@
   <printOptions/>
   <pageMargins bottom="0.5" footer="0.0" header="0.0" left="0.35" right="0.35" top="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <drawing ns1:id="rId1"/>
 </worksheet>
 </file>
 

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B5" s="17">
         <f>COUNTIF('Kernel Track'!F2:F27,"Done")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>27</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B7" s="18">
         <f>B5/B6</f>
-        <v>0.8076923076923077</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>186</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.375</v>
+        <v>0.39285714285714285</v>
       </c>
     </row>
     <row r="14">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B20" s="17">
         <f>COUNTIFS('Kernel Track'!A2:A1000,"Month 5 - Driver breadth &amp; performance",'Kernel Track'!F2:F1000,"Done")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" s="17">
         <f>COUNTIF('Kernel Track'!A2:A1000,"Month 5 - Driver breadth &amp; performance")</f>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="D20" s="24">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -3089,8 +3089,8 @@
       <c r="E23" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="11" t="s">
-        <v>26</v>
+      <c r="F23" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="G23" s="13"/>
     </row>

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B5" s="17">
         <f>COUNTIF('Kernel Track'!F2:F27,"Done")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>27</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B7" s="18">
         <f>B5/B6</f>
-        <v>0.8461538461538461</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>186</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.39285714285714285</v>
+        <v>0.4107142857142857</v>
       </c>
     </row>
     <row r="14">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B21" s="17">
         <f>COUNTIFS('Kernel Track'!A2:A1000,"Month 6 - Release hardening",'Kernel Track'!F2:F1000,"Done")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" s="17">
         <f>COUNTIF('Kernel Track'!A2:A1000,"Month 6 - Release hardening")</f>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D21" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -3110,8 +3110,8 @@
       <c r="E24" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>26</v>
+      <c r="F24" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="G24" s="13"/>
     </row>

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B5" s="17">
         <f>COUNTIF('Kernel Track'!F2:F27,"Done")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>27</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B7" s="18">
         <f>B5/B6</f>
-        <v>0.8846153846153846</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>186</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.4107142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
     </row>
     <row r="14">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B21" s="17">
         <f>COUNTIFS('Kernel Track'!A2:A1000,"Month 6 - Release hardening",'Kernel Track'!F2:F1000,"Done")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" s="17">
         <f>COUNTIF('Kernel Track'!A2:A1000,"Month 6 - Release hardening")</f>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D21" s="24">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -3131,8 +3131,8 @@
       <c r="E25" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F25" s="11" t="s">
-        <v>26</v>
+      <c r="F25" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="G25" s="13"/>
     </row>

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B5" s="17">
         <f>COUNTIF('Kernel Track'!F2:F27,"Done")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>27</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B7" s="18">
         <f>B5/B6</f>
-        <v>0.9230769230769231</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>186</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.42857142857142855</v>
+        <v>0.44642857142857145</v>
       </c>
     </row>
     <row r="14">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B21" s="17">
         <f>COUNTIFS('Kernel Track'!A2:A1000,"Month 6 - Release hardening",'Kernel Track'!F2:F1000,"Done")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" s="17">
         <f>COUNTIF('Kernel Track'!A2:A1000,"Month 6 - Release hardening")</f>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D21" s="24">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -3152,8 +3152,8 @@
       <c r="E26" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="11" t="s">
-        <v>26</v>
+      <c r="F26" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="G26" s="13"/>
     </row>

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B5" s="17">
         <f>COUNTIF('Kernel Track'!F2:F27,"Done")</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>27</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B7" s="18">
         <f>B5/B6</f>
-        <v>0.9615384615384616</v>
+        <v>1.0</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>186</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.44642857142857145</v>
+        <v>0.4642857142857143</v>
       </c>
     </row>
     <row r="14">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B21" s="17">
         <f>COUNTIFS('Kernel Track'!A2:A1000,"Month 6 - Release hardening",'Kernel Track'!F2:F1000,"Done")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" s="17">
         <f>COUNTIF('Kernel Track'!A2:A1000,"Month 6 - Release hardening")</f>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D21" s="24">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -3173,8 +3173,8 @@
       <c r="E27" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F27" s="11" t="s">
-        <v>26</v>
+      <c r="F27" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="G27" s="13"/>
     </row>

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="207">
   <si>
     <t>Month</t>
   </si>
@@ -637,6 +637,9 @@
   </si>
   <si>
     <t>Interface tasks</t>
+  </si>
+  <si>
+    <t>userland/ui-rs (libui.rlib): Color/ThemePalette (Dark/Light/HighContrast), 8-pt spacing scale, 5x7 printable ASCII typography, WidgetThemeSpec, Surface/BufferSurface32/8 drawing helpers. Linked into wm-rs.</t>
   </si>
 </sst>
 </file>
@@ -1210,7 +1213,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1256,7 +1259,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0</v>
+        <v>0.038461538461538464</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1277,7 +1280,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -1295,7 +1298,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.4642857142857143</v>
+        <v>0.48214285714285715</v>
       </c>
     </row>
     <row r="14">
@@ -1445,7 +1448,7 @@
       </c>
       <c r="B25" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 1 - Prep",'Interface Track'!F2:F1000,"Done")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 1 - Prep")</f>
@@ -1453,7 +1456,7 @@
       </c>
       <c r="D25" s="24">
         <f t="shared" ref="D25:D30" si="3">IFERROR(B25/C25,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -4175,7 +4178,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4230,10 +4233,12 @@
       <c r="E2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="13"/>
+      <c r="F2" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="3" ht="60.0" customHeight="1">
       <c r="A3" s="5" t="s">
@@ -5752,7 +5757,7 @@
   <printOptions/>
   <pageMargins bottom="0.5" footer="0.0" header="0.0" left="0.35" right="0.35" top="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <drawing ns1:id="rId1"/>
 </worksheet>
 </file>
 

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="208">
   <si>
     <t>Month</t>
   </si>
@@ -640,6 +640,9 @@
   </si>
   <si>
     <t>userland/ui-rs (libui.rlib): Color/ThemePalette (Dark/Light/HighContrast), 8-pt spacing scale, 5x7 printable ASCII typography, WidgetThemeSpec, Surface/BufferSurface32/8 drawing helpers. Linked into wm-rs.</t>
+  </si>
+  <si>
+    <t>Supervised under novainit as PID 1 via SERVICES.CFG (restart=always, trusted=yes). Delegated can_open_any_file/can_spawn capabilities. exit/logout commands hooked for session respawn.</t>
   </si>
 </sst>
 </file>
@@ -1213,7 +1216,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1259,7 +1262,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.038461538461538464</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1280,7 +1283,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -1298,7 +1301,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.48214285714285715</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14">
@@ -1448,7 +1451,7 @@
       </c>
       <c r="B25" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 1 - Prep",'Interface Track'!F2:F1000,"Done")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 1 - Prep")</f>
@@ -1456,7 +1459,7 @@
       </c>
       <c r="D25" s="24">
         <f t="shared" ref="D25:D30" si="3">IFERROR(B25/C25,0)</f>
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -4256,10 +4259,12 @@
       <c r="E3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="13"/>
+      <c r="F3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="4" ht="60.0" customHeight="1">
       <c r="A4" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="209">
   <si>
     <t>Month</t>
   </si>
@@ -643,6 +643,9 @@
   </si>
   <si>
     <t>Supervised under novainit as PID 1 via SERVICES.CFG (restart=always, trusted=yes). Delegated can_open_any_file/can_spawn capabilities. exit/logout commands hooked for session respawn.</t>
+  </si>
+  <si>
+    <t>Ported wm-rs to SYS_FB_* framebuffer graphics API. Renders 32-bit XRGB into BufferSurface32 with zero per-pixel syscalls; single-syscall present via SYS_FB_PRESENT. Tested on 1024x768 and 320x200.</t>
   </si>
 </sst>
 </file>
@@ -1216,7 +1219,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1262,7 +1265,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.07692307692307693</v>
+        <v>0.11538461538461539</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1283,7 +1286,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
@@ -1301,7 +1304,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.5</v>
+        <v>0.5178571428571429</v>
       </c>
     </row>
     <row r="14">
@@ -1468,7 +1471,7 @@
       </c>
       <c r="B26" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 2 - Compositor",'Interface Track'!F2:F1000,"Done")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 2 - Compositor")</f>
@@ -1476,7 +1479,7 @@
       </c>
       <c r="D26" s="24">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -4282,10 +4285,12 @@
       <c r="E4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="13"/>
+      <c r="F4" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="5" ht="60.0" customHeight="1">
       <c r="A5" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="210">
   <si>
     <t>Month</t>
   </si>
@@ -646,6 +646,9 @@
   </si>
   <si>
     <t>Ported wm-rs to SYS_FB_* framebuffer graphics API. Renders 32-bit XRGB into BufferSurface32 with zero per-pixel syscalls; single-syscall present via SYS_FB_PRESENT. Tested on 1024x768 and 320x200.</t>
+  </si>
+  <si>
+    <t>New no_std font module (userland/ui-rs/src/font.rs) with multiple sizes (8px Small, 16px Regular, 24px Large, scalable Vector), proportional &amp; monospace metrics, subpixel and 3x3 supersampled area antialiasing, analytical vector stroke rasterizer. Called from wm-rs compositor and UI widgets.</t>
   </si>
 </sst>
 </file>
@@ -1219,7 +1222,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1265,7 +1268,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.11538461538461539</v>
+        <v>0.15384615384615385</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1286,7 +1289,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -1304,7 +1307,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.5178571428571429</v>
+        <v>0.5357142857142857</v>
       </c>
     </row>
     <row r="14">
@@ -1471,7 +1474,7 @@
       </c>
       <c r="B26" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 2 - Compositor",'Interface Track'!F2:F1000,"Done")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 2 - Compositor")</f>
@@ -1479,7 +1482,7 @@
       </c>
       <c r="D26" s="24">
         <f t="shared" si="3"/>
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -4308,10 +4311,12 @@
       <c r="E5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="13"/>
+      <c r="F5" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="6" ht="60.0" customHeight="1">
       <c r="A6" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="211">
   <si>
     <t>Month</t>
   </si>
@@ -649,6 +649,9 @@
   </si>
   <si>
     <t>New no_std font module (userland/ui-rs/src/font.rs) with multiple sizes (8px Small, 16px Regular, 24px Large, scalable Vector), proportional &amp; monospace metrics, subpixel and 3x3 supersampled area antialiasing, analytical vector stroke rasterizer. Called from wm-rs compositor and UI widgets.</t>
+  </si>
+  <si>
+    <t>New multi-shape cursor module (userland/ui-rs/src/cursor.rs) supporting 10 shapes (Arrow, Pointer, I-Beam, Move, Resize NS/EW/NWSE/NESW, Wait, Crosshair) with 4 themes (Classic, ModernDark, ModernLight, Amber). Redesigned window chrome in userland/wm-rs/wm.rs with titlebar elevation/sheen, app icons, and control pills (Close, Maximize, Minimize).</t>
   </si>
 </sst>
 </file>
@@ -1222,7 +1225,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1268,7 +1271,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.15384615384615385</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1289,7 +1292,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -1307,7 +1310,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.5357142857142857</v>
+        <v>0.5535714285714286</v>
       </c>
     </row>
     <row r="14">
@@ -1474,7 +1477,7 @@
       </c>
       <c r="B26" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 2 - Compositor",'Interface Track'!F2:F1000,"Done")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 2 - Compositor")</f>
@@ -1482,7 +1485,7 @@
       </c>
       <c r="D26" s="24">
         <f t="shared" si="3"/>
-        <v>0.6666666666666666</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -4334,10 +4337,12 @@
       <c r="E6" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="13"/>
+      <c r="F6" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="7" ht="60.0" customHeight="1">
       <c r="A7" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="212">
   <si>
     <t>Month</t>
   </si>
@@ -652,6 +652,9 @@
   </si>
   <si>
     <t>New multi-shape cursor module (userland/ui-rs/src/cursor.rs) supporting 10 shapes (Arrow, Pointer, I-Beam, Move, Resize NS/EW/NWSE/NESW, Wait, Crosshair) with 4 themes (Classic, ModernDark, ModernLight, Amber). Redesigned window chrome in userland/wm-rs/wm.rs with titlebar elevation/sheen, app icons, and control pills (Close, Maximize, Minimize).</t>
+  </si>
+  <si>
+    <t>Persistent top-of-screen menu bar across the display (userland/ui-rs/src/menu.rs, userland/wm-rs/wm.rs). Context-aware active window menus (Terminal, Files, Editor, System), interactive dropdown overlays with pointer cursor, action dispatch via MenuClickEvent back to focused app.</t>
   </si>
 </sst>
 </file>
@@ -1225,7 +1228,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1271,7 +1274,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.19230769230769232</v>
+        <v>0.23076923076923078</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1292,7 +1295,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -1310,7 +1313,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.5535714285714286</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="14">
@@ -1494,7 +1497,7 @@
       </c>
       <c r="B27" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 3 - Core desktop apps",'Interface Track'!F2:F1000,"Done")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 3 - Core desktop apps")</f>
@@ -1502,7 +1505,7 @@
       </c>
       <c r="D27" s="24">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -4361,9 +4364,11 @@
         <v>23</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="13"/>
+        <v>27</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="8" ht="60.0" customHeight="1">
       <c r="A8" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="213">
   <si>
     <t>Month</t>
   </si>
@@ -655,6 +655,9 @@
   </si>
   <si>
     <t>Persistent top-of-screen menu bar across the display (userland/ui-rs/src/menu.rs, userland/wm-rs/wm.rs). Context-aware active window menus (Terminal, Files, Editor, System), interactive dropdown overlays with pointer cursor, action dispatch via MenuClickEvent back to focused app.</t>
+  </si>
+  <si>
+    <t>Desktop dock &amp; taskbar system (userland/ui-rs/src/dock.rs, userland/wm-rs/wm.rs). Supports pinned launchable apps (Terminal, Files, Editor, System, Settings), active window switching, minimize-to-dock and restore, running indicator pips, launch-on-click, and dynamic pinning/unpinning.</t>
   </si>
 </sst>
 </file>
@@ -1228,7 +1231,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1274,7 +1277,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.23076923076923078</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1295,7 +1298,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
@@ -1313,7 +1316,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.5714285714285714</v>
+        <v>0.5892857142857143</v>
       </c>
     </row>
     <row r="14">
@@ -1497,7 +1500,7 @@
       </c>
       <c r="B27" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 3 - Core desktop apps",'Interface Track'!F2:F1000,"Done")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 3 - Core desktop apps")</f>
@@ -1505,7 +1508,7 @@
       </c>
       <c r="D27" s="24">
         <f t="shared" si="3"/>
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -4387,9 +4390,11 @@
         <v>23</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="13"/>
+        <v>27</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="9" ht="60.0" customHeight="1">
       <c r="A9" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="214">
   <si>
     <t>Month</t>
   </si>
@@ -658,6 +658,9 @@
   </si>
   <si>
     <t>Desktop dock &amp; taskbar system (userland/ui-rs/src/dock.rs, userland/wm-rs/wm.rs). Supports pinned launchable apps (Terminal, Files, Editor, System, Settings), active window switching, minimize-to-dock and restore, running indicator pips, launch-on-click, and dynamic pinning/unpinning.</t>
+  </si>
+  <si>
+    <t>NovaOS Graphical File Manager (userland/files-rs/files.rs, ffi.rs). Ring-3 application featuring live VFS directory listing (SYS_LIST_FILES), metadata classification (Document, Config, Executable, Package, Data), mouse selection, text preview modal (SYS_OPEN/SYS_READ), file move and delete operations (SYS_WRITE_FILE, SYS_DELETE_FILE), dual view modes (List and Grid), toolbar vector action buttons, standalone framebuffer rendering, and Window 1 compositor client view.</t>
   </si>
 </sst>
 </file>
@@ -1231,7 +1234,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1277,7 +1280,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.2692307692307692</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1298,7 +1301,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -1316,7 +1319,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.5892857142857143</v>
+        <v>0.6071428571428571</v>
       </c>
     </row>
     <row r="14">
@@ -1500,7 +1503,7 @@
       </c>
       <c r="B27" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 3 - Core desktop apps",'Interface Track'!F2:F1000,"Done")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 3 - Core desktop apps")</f>
@@ -1508,7 +1511,7 @@
       </c>
       <c r="D27" s="24">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -4412,10 +4415,12 @@
       <c r="E9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="13"/>
+      <c r="F9" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="10" ht="60.0" customHeight="1">
       <c r="A10" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="215">
   <si>
     <t>Month</t>
   </si>
@@ -661,6 +661,9 @@
   </si>
   <si>
     <t>NovaOS Graphical File Manager (userland/files-rs/files.rs, ffi.rs). Ring-3 application featuring live VFS directory listing (SYS_LIST_FILES), metadata classification (Document, Config, Executable, Package, Data), mouse selection, text preview modal (SYS_OPEN/SYS_READ), file move and delete operations (SYS_WRITE_FILE, SYS_DELETE_FILE), dual view modes (List and Grid), toolbar vector action buttons, standalone framebuffer rendering, and Window 1 compositor client view.</t>
+  </si>
+  <si>
+    <t>NovaOS Graphical Settings App (userland/settings-rs/settings.rs, ffi.rs). Modular plugin-panel architecture supporting System &amp; Identity (SYSTEM.CFG), Accounts &amp; Users (USERS.CFG), Services &amp; Startup (SERVICES.CFG), Network &amp; Firewall (FIREWALL.CFG), and Display &amp; Themes. Features interactive sidebar navigation, field editing, binary/text serialization, BufferSurface32 rendering, and Window 4 compositor client view.</t>
   </si>
 </sst>
 </file>
@@ -1234,7 +1237,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1280,7 +1283,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.3076923076923077</v>
+        <v>0.34615384615384615</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1301,7 +1304,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -1319,7 +1322,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.6071428571428571</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="14">
@@ -1503,7 +1506,7 @@
       </c>
       <c r="B27" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 3 - Core desktop apps",'Interface Track'!F2:F1000,"Done")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 3 - Core desktop apps")</f>
@@ -1511,7 +1514,7 @@
       </c>
       <c r="D27" s="24">
         <f t="shared" si="3"/>
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -4438,10 +4441,12 @@
       <c r="E10" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="13"/>
+      <c r="F10" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="11" ht="60.0" customHeight="1">
       <c r="A11" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="216">
   <si>
     <t>Month</t>
   </si>
@@ -664,6 +664,9 @@
   </si>
   <si>
     <t>NovaOS Graphical Settings App (userland/settings-rs/settings.rs, ffi.rs). Modular plugin-panel architecture supporting System &amp; Identity (SYSTEM.CFG), Accounts &amp; Users (USERS.CFG), Services &amp; Startup (SERVICES.CFG), Network &amp; Firewall (FIREWALL.CFG), and Display &amp; Themes. Features interactive sidebar navigation, field editing, binary/text serialization, BufferSurface32 rendering, and Window 4 compositor client view.</t>
+  </si>
+  <si>
+    <t>NovaOS In-Window Terminal App (userland/term-rs/term.rs, ffi.rs). Full virtual terminal emulator running the interactive shell and command dispatcher (help, ls, cat, echo, clear, date, uname, whoami, pwd, history, run) in a real resizable window. Features ANSI 16-color SGR and escape parsing, cell-aligned cursor tracking, line editing with command history (Up/Down) and Tab completion, dynamic column/row rewrapping, scrollback buffer, zero per-pixel syscall BufferSurface32 rendering, and Window 0 compositor client view.</t>
   </si>
 </sst>
 </file>
@@ -1218,7 +1221,7 @@
         <v>24</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>41</v>
@@ -1367,15 +1370,15 @@
       </c>
       <c r="B17" s="17">
         <f>COUNTIFS('Kernel Track'!A2:A1000,"Month 2 - Graphics foundation",'Kernel Track'!F2:F1000,"Done")</f>
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="C17" s="17">
         <f>COUNTIF('Kernel Track'!A2:A1000,"Month 2 - Graphics foundation")</f>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D17" s="24">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.6428571428571429</v>
       </c>
     </row>
     <row r="18">
@@ -4464,10 +4467,12 @@
       <c r="E11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="13"/>
+      <c r="F11" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="12" ht="60.0" customHeight="1">
       <c r="A12" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="217">
   <si>
     <t>Month</t>
   </si>
@@ -667,6 +667,9 @@
   </si>
   <si>
     <t>NovaOS In-Window Terminal App (userland/term-rs/term.rs, ffi.rs). Full virtual terminal emulator running the interactive shell and command dispatcher (help, ls, cat, echo, clear, date, uname, whoami, pwd, history, run) in a real resizable window. Features ANSI 16-color SGR and escape parsing, cell-aligned cursor tracking, line editing with command history (Up/Down) and Tab completion, dynamic column/row rewrapping, scrollback buffer, zero per-pixel syscall BufferSurface32 rendering, and Window 0 compositor client view.</t>
+  </si>
+  <si>
+    <t>NovaOS Graphical Text Editor App (userland/edit-rs/editor.rs, ffi.rs). Multi-line text buffer model with line insertion, line splitting, backspace line merging, cursor navigation, and boundary clamping. Features VFS file I/O operations (SYS_OPEN, SYS_READ, SYS_CLOSE, SYS_WRITE_FILE), advanced multi-size typography showcase (Mono 8x16, Sans 8x16, Small 8x8, Large 12x24), line numbers gutter with active line accentuation, lightweight code syntax highlighting, top interactive toolbar ([New], [Open], [Save], [Cut], [Copy], [Paste], [Font: ...]), bottom status bar with statistics, zero per-pixel syscall BufferSurface32 rendering, and Window 2 compositor client view.</t>
   </si>
 </sst>
 </file>
@@ -1240,7 +1243,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1286,7 +1289,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.34615384615384615</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1307,7 +1310,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
@@ -1325,7 +1328,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.625</v>
+        <v>0.6607142857142857</v>
       </c>
     </row>
     <row r="14">
@@ -1509,7 +1512,7 @@
       </c>
       <c r="B27" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 3 - Core desktop apps",'Interface Track'!F2:F1000,"Done")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C27" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 3 - Core desktop apps")</f>
@@ -1517,7 +1520,7 @@
       </c>
       <c r="D27" s="24">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -4490,10 +4493,12 @@
       <c r="E12" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="13"/>
+      <c r="F12" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="13" ht="60.0" customHeight="1">
       <c r="A13" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="218">
   <si>
     <t>Month</t>
   </si>
@@ -670,6 +670,9 @@
   </si>
   <si>
     <t>NovaOS Graphical Text Editor App (userland/edit-rs/editor.rs, ffi.rs). Multi-line text buffer model with line insertion, line splitting, backspace line merging, cursor navigation, and boundary clamping. Features VFS file I/O operations (SYS_OPEN, SYS_READ, SYS_CLOSE, SYS_WRITE_FILE), advanced multi-size typography showcase (Mono 8x16, Sans 8x16, Small 8x8, Large 12x24), line numbers gutter with active line accentuation, lightweight code syntax highlighting, top interactive toolbar ([New], [Open], [Save], [Cut], [Copy], [Paste], [Font: ...]), bottom status bar with statistics, zero per-pixel syscall BufferSurface32 rendering, and Window 2 compositor client view.</t>
+  </si>
+  <si>
+    <t>NovaOS Graphical Software Store &amp; App Launcher (userland/store-rs/store.rs, crypto.rs, ffi.rs, STORE.ELF). Pure #![no_std] graphical front-end for the package system. Features package manifest parsing, HMAC-SHA256 cryptographic signature verification (RFC 2104/6234), install database management (INSTALL.DB), package installation and removal, direct application launching via SYS_EXEC, in-kernel HTTP package repository telemetry &amp; controls via SYS_PKGREPO_CTL (status, port 8080, requests, packages served), category filtering (Productivity, Games, Utilities, System), search query matching, package inspector panel, zero per-pixel syscall BufferSurface32 rendering, and Window 3 compositor client view.</t>
   </si>
 </sst>
 </file>
@@ -1196,7 +1199,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1243,7 +1246,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1289,7 +1292,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.4230769230769231</v>
+        <v>0.46153846153846156</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1310,7 +1313,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -1328,7 +1331,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.6607142857142857</v>
+        <v>0.6785714285714286</v>
       </c>
     </row>
     <row r="14">
@@ -1512,7 +1515,7 @@
       </c>
       <c r="B27" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 3 - Core desktop apps",'Interface Track'!F2:F1000,"Done")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 3 - Core desktop apps")</f>
@@ -1520,7 +1523,7 @@
       </c>
       <c r="D27" s="24">
         <f t="shared" si="3"/>
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -2621,7 +2624,7 @@
   <printOptions/>
   <pageMargins bottom="0.5" footer="0.0" header="0.0" left="0.4" right="0.4" top="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
-  <drawing ns1:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4208,7 +4211,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4517,9 +4520,11 @@
         <v>23</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="13"/>
+        <v>27</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="14" ht="60.0" customHeight="1">
       <c r="A14" s="5" t="s">
@@ -5807,7 +5812,7 @@
   <printOptions/>
   <pageMargins bottom="0.5" footer="0.0" header="0.0" left="0.35" right="0.35" top="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
-  <drawing ns1:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="219">
   <si>
     <t>Month</t>
   </si>
@@ -673,6 +673,9 @@
   </si>
   <si>
     <t>NovaOS Graphical Software Store &amp; App Launcher (userland/store-rs/store.rs, crypto.rs, ffi.rs, STORE.ELF). Pure #![no_std] graphical front-end for the package system. Features package manifest parsing, HMAC-SHA256 cryptographic signature verification (RFC 2104/6234), install database management (INSTALL.DB), package installation and removal, direct application launching via SYS_EXEC, in-kernel HTTP package repository telemetry &amp; controls via SYS_PKGREPO_CTL (status, port 8080, requests, packages served), category filtering (Productivity, Games, Utilities, System), search query matching, package inspector panel, zero per-pixel syscall BufferSurface32 rendering, and Window 3 compositor client view.</t>
+  </si>
+  <si>
+    <t>NovaOS Graphical Login Screen and Display Manager (userland/login-rs/login.rs, ffi.rs, LOGIN.ELF). Pure #![no_std] privileged ring-3 display manager running before the desktop environment. Features persistent user account parsing from USERS.CFG (NVUS magic) and SYSTEM.CFG (NVCF magic), authentication and identity isolation via SYS_LOGIN and SYS_GETUID (persisted uid 700, admin uid 800), multi-account switcher with user avatar badges and custom user entry, secure password input with bullet masking and show/hide toggle, real-time clock integration (SYS_RTC_READ) with hero digital clock and calendar date, session selector (Window Manager WM.ELF or Console Shell SHELL.ELF via SYS_EXEC), power management controls (ACPI shutdown via SYS_SHUTDOWN and reboot), zero per-pixel syscall BufferSurface32 rasterization conforming to NovaOS Design System.</t>
   </si>
 </sst>
 </file>
@@ -1199,7 +1202,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1246,7 +1249,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1292,7 +1295,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.46153846153846156</v>
+        <v>0.5</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1313,7 +1316,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -1331,7 +1334,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.6785714285714286</v>
+        <v>0.6964285714285714</v>
       </c>
     </row>
     <row r="14">
@@ -1515,7 +1518,7 @@
       </c>
       <c r="B27" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 3 - Core desktop apps",'Interface Track'!F2:F1000,"Done")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C27" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 3 - Core desktop apps")</f>
@@ -1523,7 +1526,7 @@
       </c>
       <c r="D27" s="24">
         <f t="shared" si="3"/>
-        <v>0.875</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -2624,7 +2627,7 @@
   <printOptions/>
   <pageMargins bottom="0.5" footer="0.0" header="0.0" left="0.4" right="0.4" top="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <drawing ns1:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4211,7 +4214,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4543,9 +4546,11 @@
         <v>23</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="13"/>
+        <v>27</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="15" ht="60.0" customHeight="1">
       <c r="A15" s="5" t="s">
@@ -5812,7 +5817,7 @@
   <printOptions/>
   <pageMargins bottom="0.5" footer="0.0" header="0.0" left="0.35" right="0.35" top="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <drawing ns1:id="rId1"/>
 </worksheet>
 </file>
 

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="220">
   <si>
     <t>Month</t>
   </si>
@@ -676,6 +676,9 @@
   </si>
   <si>
     <t>NovaOS Graphical Login Screen and Display Manager (userland/login-rs/login.rs, ffi.rs, LOGIN.ELF). Pure #![no_std] privileged ring-3 display manager running before the desktop environment. Features persistent user account parsing from USERS.CFG (NVUS magic) and SYSTEM.CFG (NVCF magic), authentication and identity isolation via SYS_LOGIN and SYS_GETUID (persisted uid 700, admin uid 800), multi-account switcher with user avatar badges and custom user entry, secure password input with bullet masking and show/hide toggle, real-time clock integration (SYS_RTC_READ) with hero digital clock and calendar date, session selector (Window Manager WM.ELF or Console Shell SHELL.ELF via SYS_EXEC), power management controls (ACPI shutdown via SYS_SHUTDOWN and reboot), zero per-pixel syscall BufferSurface32 rasterization conforming to NovaOS Design System.</t>
+  </si>
+  <si>
+    <t>NovaOS Network &amp; Firewall Settings Panel in Settings App (userland/settings-rs/settings.rs, ffi.rs, SETTINGS.ELF). Pure #![no_std] graphical control panel plugged into the modular Settings shell. Live synchronization with kernel-side stateful packet filter via SYS_FW_INFO and SYS_FW_CTL (NOVA_FW_OP_GET_RULE, NOVA_FW_OP_SET_POLICY, NOVA_FW_OP_ADD_RULE, NOVA_FW_OP_DEL_RULE, NOVA_FW_OP_FLUSH_RULES, NOVA_FW_OP_FLUSH_CONNS). Displays live firewall status, inbound/outbound default policy toggles, full rule criteria table (Action, Dir, Proto, Source/Dest CIDR, Port ranges, TCP/connection state, hit counters), quick preset buttons (+ SSH 22, + HTTP 80), and rule deletion. Features full network adapter hardware and IPv4 addressing configuration (eth0 RTL8139 / Virtio-Net, MAC 52:54:00:12:34:56, 10.0.2.15/24, gateway 10.0.2.2, DNS 10.0.2.3), bidirectional persistence to FIREWALL.CFG, and zero per-pixel syscall BufferSurface32 rendering across 3 interactive sub-tabs.</t>
   </si>
 </sst>
 </file>
@@ -1249,7 +1252,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1295,7 +1298,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.5</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1316,7 +1319,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -1334,7 +1337,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.6964285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="14">
@@ -1535,7 +1538,7 @@
       </c>
       <c r="B28" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 4 - Server &amp; admin UI",'Interface Track'!F2:F1000,"Done")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 4 - Server &amp; admin UI")</f>
@@ -1543,7 +1546,7 @@
       </c>
       <c r="D28" s="24">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -4569,9 +4572,11 @@
         <v>23</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="13"/>
+        <v>27</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="16" ht="60.0" customHeight="1">
       <c r="A16" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="221">
   <si>
     <t>Month</t>
   </si>
@@ -679,6 +679,9 @@
   </si>
   <si>
     <t>NovaOS Network &amp; Firewall Settings Panel in Settings App (userland/settings-rs/settings.rs, ffi.rs, SETTINGS.ELF). Pure #![no_std] graphical control panel plugged into the modular Settings shell. Live synchronization with kernel-side stateful packet filter via SYS_FW_INFO and SYS_FW_CTL (NOVA_FW_OP_GET_RULE, NOVA_FW_OP_SET_POLICY, NOVA_FW_OP_ADD_RULE, NOVA_FW_OP_DEL_RULE, NOVA_FW_OP_FLUSH_RULES, NOVA_FW_OP_FLUSH_CONNS). Displays live firewall status, inbound/outbound default policy toggles, full rule criteria table (Action, Dir, Proto, Source/Dest CIDR, Port ranges, TCP/connection state, hit counters), quick preset buttons (+ SSH 22, + HTTP 80), and rule deletion. Features full network adapter hardware and IPv4 addressing configuration (eth0 RTL8139 / Virtio-Net, MAC 52:54:00:12:34:56, 10.0.2.15/24, gateway 10.0.2.2, DNS 10.0.2.3), bidirectional persistence to FIREWALL.CFG, and zero per-pixel syscall BufferSurface32 rendering across 3 interactive sub-tabs.</t>
+  </si>
+  <si>
+    <t>NovaOS User and Permissions Management Panel in Settings App (userland/settings-rs/settings.rs, crypto.rs, ffi.rs, SETTINGS.ELF). Pure #![no_std] graphical useradd equivalent and account administration panel plugged into the modular Settings shell. Full binary read/write interoperability with USERS.CFG (magic NVUS, 716 bytes, up to 8 accounts) matching kernel/rust/users.rs format. Features standalone cryptographic authentication with RFC 6234 SHA-256, RFC 2104 HMAC-SHA256, and RFC 8018 PBKDF2-HMAC-SHA256 with 4096 iterations and per-account salt derivation. Graphical account list with avatar badges, role indicators, and inspector card. Graphical useradd modal with quick presets (Alice, Bob, Operator, Guest), password masking, confirmation validation, and automatic UID assignment. Role switcher toggling Administrator (gid 0) vs Standard User (gid = uid / 1000) with last-administrator safeguard preventing accidental lockout. Minimum account deletion safeguard ensuring system retains at least one account. Zero per-pixel syscall BufferSurface32 rendering.</t>
   </si>
 </sst>
 </file>
@@ -1252,7 +1255,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1298,7 +1301,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.5384615384615384</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1319,7 +1322,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
@@ -1337,7 +1340,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.7142857142857143</v>
+        <v>0.7321428571428571</v>
       </c>
     </row>
     <row r="14">
@@ -1538,7 +1541,7 @@
       </c>
       <c r="B28" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 4 - Server &amp; admin UI",'Interface Track'!F2:F1000,"Done")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 4 - Server &amp; admin UI")</f>
@@ -1546,7 +1549,7 @@
       </c>
       <c r="D28" s="24">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -4595,9 +4598,11 @@
         <v>23</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="13"/>
+        <v>27</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="17" ht="60.0" customHeight="1">
       <c r="A17" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="222">
   <si>
     <t>Month</t>
   </si>
@@ -682,6 +682,9 @@
   </si>
   <si>
     <t>NovaOS User and Permissions Management Panel in Settings App (userland/settings-rs/settings.rs, crypto.rs, ffi.rs, SETTINGS.ELF). Pure #![no_std] graphical useradd equivalent and account administration panel plugged into the modular Settings shell. Full binary read/write interoperability with USERS.CFG (magic NVUS, 716 bytes, up to 8 accounts) matching kernel/rust/users.rs format. Features standalone cryptographic authentication with RFC 6234 SHA-256, RFC 2104 HMAC-SHA256, and RFC 8018 PBKDF2-HMAC-SHA256 with 4096 iterations and per-account salt derivation. Graphical account list with avatar badges, role indicators, and inspector card. Graphical useradd modal with quick presets (Alice, Bob, Operator, Guest), password masking, confirmation validation, and automatic UID assignment. Role switcher toggling Administrator (gid 0) vs Standard User (gid = uid / 1000) with last-administrator safeguard preventing accidental lockout. Minimum account deletion safeguard ensuring system retains at least one account. Zero per-pixel syscall BufferSurface32 rendering.</t>
+  </si>
+  <si>
+    <t>NovaOS Graphical Structured Kernel Log Viewer (userland/klog-rs/klog.rs, ffi.rs, build.sh, KLOG.ELF). Pure #![no_std] ring-3 graphical structured kernel log viewer for NovaOS. Integrates with the structured kernel logging subsystem via SYS_KLOG_READ (75), SYS_KLOG_WRITE (76), and SYS_KLOG_INFO (77). Features live telemetry tracking (total logged, dropped packets, buffer capacity, entry count), interactive toolbar controls ([Pause/Resume live stream], [Refresh], [+ Marker], [Clear view]), syslog severity selector pills ([ALL], [ERR+], [WARN+], [INFO+], [DEBUG]), facility filtering chips ([ALL], [kernel], [driver], [init], [net], [fs]), real-time keyword search with in-line substring hit highlighting, color-coded severity badges (Emerg, Alert, Crit, Error, Warn, Notice, Info, Debug), dedicated bottom Inspector pane with complete unclipped message, timestamp, PID, and diagnostic triage hints, zero-syscall BufferSurface32 rasterization, and BSS-backed state management ensuring 0 bytes of stack exhaustion in the 16KB userland stack.</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1258,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1301,7 +1304,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.5769230769230769</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1322,7 +1325,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -1340,7 +1343,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.7321428571428571</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="14">
@@ -1541,7 +1544,7 @@
       </c>
       <c r="B28" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 4 - Server &amp; admin UI",'Interface Track'!F2:F1000,"Done")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 4 - Server &amp; admin UI")</f>
@@ -1549,7 +1552,7 @@
       </c>
       <c r="D28" s="24">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -4620,10 +4623,12 @@
       <c r="E17" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="13"/>
+      <c r="F17" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="18" ht="60.0" customHeight="1">
       <c r="A18" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="223">
   <si>
     <t>Month</t>
   </si>
@@ -685,6 +685,9 @@
   </si>
   <si>
     <t>NovaOS Graphical Structured Kernel Log Viewer (userland/klog-rs/klog.rs, ffi.rs, build.sh, KLOG.ELF). Pure #![no_std] ring-3 graphical structured kernel log viewer for NovaOS. Integrates with the structured kernel logging subsystem via SYS_KLOG_READ (75), SYS_KLOG_WRITE (76), and SYS_KLOG_INFO (77). Features live telemetry tracking (total logged, dropped packets, buffer capacity, entry count), interactive toolbar controls ([Pause/Resume live stream], [Refresh], [+ Marker], [Clear view]), syslog severity selector pills ([ALL], [ERR+], [WARN+], [INFO+], [DEBUG]), facility filtering chips ([ALL], [kernel], [driver], [init], [net], [fs]), real-time keyword search with in-line substring hit highlighting, color-coded severity badges (Emerg, Alert, Crit, Error, Warn, Notice, Info, Debug), dedicated bottom Inspector pane with complete unclipped message, timestamp, PID, and diagnostic triage hints, zero-syscall BufferSurface32 rasterization, and BSS-backed state management ensuring 0 bytes of stack exhaustion in the 16KB userland stack.</t>
+  </si>
+  <si>
+    <t>NovaOS Graphical Service Manager Panel (userland/settings-rs/settings.rs, ffi.rs, build.sh, SETTINGS.ELF). Pure #![no_std] ring-3 administrative panel integrated into the Settings application for real-time service supervision and lifecycle management. Communicates with PID 1 (novainit-rs) via dedicated bidirectional syscall SYS_SERVICE_STATUS (82) supporting NOVA_SVC_OP_QUERY, NOVA_SVC_OP_PUBLISH, NOVA_SVC_OP_CONTROL, and NOVA_SVC_OP_GET_ACTION. Features a dual-mode interface (Live Supervision Dashboard and SERVICES.CFG declarative editor), telemetry banner (Supervisor PID 1, total, running, restarting, crashed, stopped counts), live service list with color-coded status pills (RUNNING green, RESTARTING amber, CRASHED red, WAITING cyan, STOPPED gray), detailed service inspector (full command line, dependency chain, restart counter N/20, privilege badge Trusted vs Standard), and interactive operator lifecycle controls ([Restart Service], [Stop Service], [Start Service], [Refresh]). Rasterized directly onto BufferSurface32 without per-pixel syscall overhead, backed entirely by static BSS memory ensuring 0-byte stack exhaustion within the 16KB userland stack budget.</t>
   </si>
 </sst>
 </file>
@@ -1258,7 +1261,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1304,7 +1307,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.6153846153846154</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1325,7 +1328,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
@@ -1343,7 +1346,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.75</v>
+        <v>0.7678571428571429</v>
       </c>
     </row>
     <row r="14">
@@ -1544,7 +1547,7 @@
       </c>
       <c r="B28" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 4 - Server &amp; admin UI",'Interface Track'!F2:F1000,"Done")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 4 - Server &amp; admin UI")</f>
@@ -1552,7 +1555,7 @@
       </c>
       <c r="D28" s="24">
         <f t="shared" si="3"/>
-        <v>0.75</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -4646,10 +4649,12 @@
       <c r="E18" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="13"/>
+      <c r="F18" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="19" ht="60.0" customHeight="1">
       <c r="A19" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="226">
   <si>
     <t>Month</t>
   </si>
@@ -694,6 +694,9 @@
   </si>
   <si>
     <t>NovaOS Graphical Activity &amp; Performance Monitor App (userland/actmon-rs/actmon.rs, ffi.rs, build.sh, ACTMON.ELF, SYSINFO.ELF, userland/libc/include/nova_proc_abi.h, kernel/rust/procman.rs). Pure #![no_std] ring-3 graphical system activity monitor querying scheduler state and physical memory telemetry via dedicated syscall SYS_PROC_INFO (84) supporting NOVA_PROC_OP_GET_SYSINFO, NOVA_PROC_OP_GET_TABLE, and NOVA_PROC_OP_GET_ENTRY. Features a 4-view tabbed interface ([Processes], [CPU &amp; Performance], [Memory &amp; System], [System Info]), real-time telemetry banner cards (CPU usage gauge with live sparkline trend, physical memory gauge with used/total MB and percentage, process count breakdown across Total/Running/User/Kernel, and SMP active cores), 4 category filter chips (All, Apps (User), Kernel Tasks, Active (&gt;0%)), real-time substring search filtering, interactive column sorting (PID, Name, CPU %, Memory footprint), detailed process inspector card (PID, Name, execution state, security context UID/GID, memory pages, heap allocation, CPU ticks, window quota usage %), and responsive status bar with live summary. Rasterized directly onto BufferSurface32 without per-pixel syscall overhead, backed entirely by static BSS buffers guaranteeing 0-byte stack exhaustion within the 16KB userland stack budget. Verified via make actmon-test (10 host tests: 4 kernel + 6 app) and automated QEMU boot test.</t>
+  </si>
+  <si>
+    <t>NovaOS Global Accessibility Architecture &amp; Display Panel (userland/ui-rs/src/access.rs, color.rs, cursor.rs, font.rs, lib.rs, userland/wm-rs/wm.rs, ffi.rs, WM.ELF, userland/settings-rs/settings.rs, SETTINGS.ELF, tools/fixtures/ACCESS.CFG). Pure #![no_std] global accessibility subsystem supporting dynamic typography scaling and high-contrast visuals for low-vision accessibility. Features 4 font scaling tiers (Normal 100%, Medium 125%, Large 150%, Extra Large 200%) dynamically resizing line heights, character advances, and glyph metrics, Theme::HighContrast palette conforming to WCAG 2.1 AAA contrast ratios (&gt;7.0:1 text, pure #000000 background, pure #FFFFFF text and active titlebars, #FFFF00 focus rings, bold accents, disabled drop shadows, and 2px window borders), and high-visibility cursor (CursorTheme::HighContrast with bright yellow #FFFF00 interior and pure black outline). Fully integrated into the window manager (Wm::apply_accessibility_config, set_font_scale, set_theme) dynamically scaling titlebars, menubars, and taskbars, and into the Settings application (PanelKind::Display 'Display &amp; Accessibility') with live typography preview cards, font scale buttons, high-contrast toggle, cursor style cycler, and 64-byte persistent binary configuration (ACCESS.CFG with NVAC magic and 16-bit CRC checksum). Zero per-pixel syscall overhead rasterized directly onto BufferSurface32 and backed by static BSS memory within the 16KB userland stack budget. Verified via make ui-test (23 tests), make wm-test (10 tests), make settings-test (21 tests), and automated QEMU boot test.</t>
   </si>
 </sst>
 </file>
@@ -1267,7 +1270,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1313,7 +1316,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.7307692307692307</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1334,7 +1337,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
@@ -1352,7 +1355,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.8035714285714286</v>
+        <v>0.8214285714285714</v>
       </c>
     </row>
     <row r="14">
@@ -1570,7 +1573,7 @@
       </c>
       <c r="B29" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 5 - Power-user &amp; system apps",'Interface Track'!F2:F1000,"Done")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 5 - Power-user &amp; system apps")</f>
@@ -1578,7 +1581,7 @@
       </c>
       <c r="D29" s="24">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -4724,10 +4727,12 @@
       <c r="E21" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F21" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="13"/>
+      <c r="F21" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="22" ht="60.0" customHeight="1">
       <c r="A22" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="227">
   <si>
     <t>Month</t>
   </si>
@@ -697,6 +697,9 @@
   </si>
   <si>
     <t>NovaOS Global Accessibility Architecture &amp; Display Panel (userland/ui-rs/src/access.rs, color.rs, cursor.rs, font.rs, lib.rs, userland/wm-rs/wm.rs, ffi.rs, WM.ELF, userland/settings-rs/settings.rs, SETTINGS.ELF, tools/fixtures/ACCESS.CFG). Pure #![no_std] global accessibility subsystem supporting dynamic typography scaling and high-contrast visuals for low-vision accessibility. Features 4 font scaling tiers (Normal 100%, Medium 125%, Large 150%, Extra Large 200%) dynamically resizing line heights, character advances, and glyph metrics, Theme::HighContrast palette conforming to WCAG 2.1 AAA contrast ratios (&gt;7.0:1 text, pure #000000 background, pure #FFFFFF text and active titlebars, #FFFF00 focus rings, bold accents, disabled drop shadows, and 2px window borders), and high-visibility cursor (CursorTheme::HighContrast with bright yellow #FFFF00 interior and pure black outline). Fully integrated into the window manager (Wm::apply_accessibility_config, set_font_scale, set_theme) dynamically scaling titlebars, menubars, and taskbars, and into the Settings application (PanelKind::Display 'Display &amp; Accessibility') with live typography preview cards, font scale buttons, high-contrast toggle, cursor style cycler, and 64-byte persistent binary configuration (ACCESS.CFG with NVAC magic and 16-bit CRC checksum). Zero per-pixel syscall overhead rasterized directly onto BufferSurface32 and backed by static BSS memory within the 16KB userland stack budget. Verified via make ui-test (23 tests), make wm-test (10 tests), make settings-test (21 tests), and automated QEMU boot test.</t>
+  </si>
+  <si>
+    <t>NovaOS Multi-Window Snapping Polish &amp; Tiling Subsystem (userland/wm-rs/wm.rs, ffi.rs, WM.ELF, userland/ui-rs/src/menu.rs). Pure #![no_std] refined window snapping and tiling engine featuring expanded SnapState (Normal, Left, Right, Maximize, TopLeft, TopRight, BottomLeft, BottomRight), panel-aware WorkArea and multi-monitor-ready MonitorGeometry abstractions respecting top menubar (y=24) and bottom taskbar (y=732), smoother edges with gapless non-overlapping quadrant and half coverage, interactive snap preview ghost outline overlay with accent stroke, titlebar Maximize button toggle ('[]') with floating pre_snap geometry preservation, proportional cursor placement on un-snap preventing abrupt jumps, double-click titlebar maximize toggle, automated tiling modes (TileMode::SideBySide, Grid2x2, Cascade), and menu action dispatch (ACTION_WINDOW_SNAP_LEFT/RIGHT/TOP_LEFT/TOP_RIGHT/BOTTOM_LEFT/BOTTOM_RIGHT/RESTORE/TILE_GRID/CASCADE). Fully verified via make wm-test (17 host tests) and automated QEMU boot test.</t>
   </si>
 </sst>
 </file>
@@ -1270,7 +1273,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1316,7 +1319,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.7692307692307693</v>
+        <v>0.8076923076923077</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1337,7 +1340,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -1355,7 +1358,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.8214285714285714</v>
+        <v>0.8392857142857143</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1576,7 @@
       </c>
       <c r="B29" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 5 - Power-user &amp; system apps",'Interface Track'!F2:F1000,"Done")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C29" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 5 - Power-user &amp; system apps")</f>
@@ -1581,7 +1584,7 @@
       </c>
       <c r="D29" s="24">
         <f t="shared" si="3"/>
-        <v>0.75</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -4750,10 +4753,12 @@
       <c r="E22" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="13"/>
+      <c r="F22" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="23" ht="60.0" customHeight="1">
       <c r="A23" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
   <si>
     <t>Month</t>
   </si>
@@ -700,6 +700,9 @@
   </si>
   <si>
     <t>NovaOS Multi-Window Snapping Polish &amp; Tiling Subsystem (userland/wm-rs/wm.rs, ffi.rs, WM.ELF, userland/ui-rs/src/menu.rs). Pure #![no_std] refined window snapping and tiling engine featuring expanded SnapState (Normal, Left, Right, Maximize, TopLeft, TopRight, BottomLeft, BottomRight), panel-aware WorkArea and multi-monitor-ready MonitorGeometry abstractions respecting top menubar (y=24) and bottom taskbar (y=732), smoother edges with gapless non-overlapping quadrant and half coverage, interactive snap preview ghost outline overlay with accent stroke, titlebar Maximize button toggle ('[]') with floating pre_snap geometry preservation, proportional cursor placement on un-snap preventing abrupt jumps, double-click titlebar maximize toggle, automated tiling modes (TileMode::SideBySide, Grid2x2, Cascade), and menu action dispatch (ACTION_WINDOW_SNAP_LEFT/RIGHT/TOP_LEFT/TOP_RIGHT/BOTTOM_LEFT/BOTTOM_RIGHT/RESTORE/TILE_GRID/CASCADE). Fully verified via make wm-test (17 host tests) and automated QEMU boot test.</t>
+  </si>
+  <si>
+    <t>NovaOS Graphical Installer Flow (userland/installer-rs/installer.rs, ffi.rs, crypto.rs, build.sh, tools/fixtures/INSTALL.ELF). Pure #![no_std] ring-3 graphical installer wizard walking the user through live OS installation. Features a 6-step guided wizard state machine: 1) Welcome &amp; System Overview with live hardware autodetection (x86 32-bit SMP cores, physical RAM, ATA/VirtIO/NVMe block devices, VESA linear framebuffer) and hardware prerequisite validation; 2) Target Disk Selection &amp; Partition Layout with block device selector (/dev/ata0, /dev/vda, /dev/nvme0n1), partition presets (Standard 64/32/4/1 MB, Minimal 32/16/2/1 MB, Workstation 128/64/8/2 MB), proportional visual color-coded partition bar gauge, and SYS_DISK_INSTALL dry-run geometry validation; 3) User Account &amp; System Configuration with hostname input (novaos), administrator username (admin), password masking with confirmation matching and strength scoring, pure #![no_std] PBKDF2-HMAC-SHA256 password hashing with random salt synthesis for USERS.CFG (NVUS magic), initial SYSTEM.CFG generation (NVCF magic), and default desktop session selector (WM.ELF vs SHELL.ELF); 4) Summary &amp; Pre-Install Confirmation reviewing complete blueprint with prominent caution warning and authorization safety toggle; 5) Live Installation Progress engine driving SYS_DISK_INSTALL with animated 0-100% progress bar, stage indicator checklists, and live scrolling status log; 6) Installation Success completion screen with completion badge, summary metrics, and [Reboot System] / [Quit to Shell] actions. Direct BufferSurface32 rendering with zero per-pixel syscalls, backed by static BSS memory within the 16KB userland stack limit. Includes kernel FAT32 cluster allocator optimization in kernel/fs/fat32.c eliminating sector scan I/O bottleneck. Verified via make installer-test (10 host tests) and automated QEMU boot test (265/265 assertions passing).</t>
   </si>
 </sst>
 </file>
@@ -1273,7 +1276,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1319,7 +1322,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.8076923076923077</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1340,7 +1343,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -1358,7 +1361,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.8392857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="14">
@@ -1593,7 +1596,7 @@
       </c>
       <c r="B30" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 6 - First impressions",'Interface Track'!F2:F1000,"Done")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 6 - First impressions")</f>
@@ -1601,7 +1604,7 @@
       </c>
       <c r="D30" s="24">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -4776,10 +4779,12 @@
       <c r="E23" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F23" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="13"/>
+      <c r="F23" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="24" ht="60.0" customHeight="1">
       <c r="A24" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="229">
   <si>
     <t>Month</t>
   </si>
@@ -703,6 +703,9 @@
   </si>
   <si>
     <t>NovaOS Graphical Installer Flow (userland/installer-rs/installer.rs, ffi.rs, crypto.rs, build.sh, tools/fixtures/INSTALL.ELF). Pure #![no_std] ring-3 graphical installer wizard walking the user through live OS installation. Features a 6-step guided wizard state machine: 1) Welcome &amp; System Overview with live hardware autodetection (x86 32-bit SMP cores, physical RAM, ATA/VirtIO/NVMe block devices, VESA linear framebuffer) and hardware prerequisite validation; 2) Target Disk Selection &amp; Partition Layout with block device selector (/dev/ata0, /dev/vda, /dev/nvme0n1), partition presets (Standard 64/32/4/1 MB, Minimal 32/16/2/1 MB, Workstation 128/64/8/2 MB), proportional visual color-coded partition bar gauge, and SYS_DISK_INSTALL dry-run geometry validation; 3) User Account &amp; System Configuration with hostname input (novaos), administrator username (admin), password masking with confirmation matching and strength scoring, pure #![no_std] PBKDF2-HMAC-SHA256 password hashing with random salt synthesis for USERS.CFG (NVUS magic), initial SYSTEM.CFG generation (NVCF magic), and default desktop session selector (WM.ELF vs SHELL.ELF); 4) Summary &amp; Pre-Install Confirmation reviewing complete blueprint with prominent caution warning and authorization safety toggle; 5) Live Installation Progress engine driving SYS_DISK_INSTALL with animated 0-100% progress bar, stage indicator checklists, and live scrolling status log; 6) Installation Success completion screen with completion badge, summary metrics, and [Reboot System] / [Quit to Shell] actions. Direct BufferSurface32 rendering with zero per-pixel syscalls, backed by static BSS memory within the 16KB userland stack limit. Includes kernel FAT32 cluster allocator optimization in kernel/fs/fat32.c eliminating sector scan I/O bottleneck. Verified via make installer-test (10 host tests) and automated QEMU boot test (265/265 assertions passing).</t>
+  </si>
+  <si>
+    <t>NovaOS Graphical Crash Reporter &amp; Diagnostic Inspector (userland/crashrep-rs/crashrep.rs, parser.rs, ffi.rs, build.sh, tools/fixtures/CRASHREP.ELF, tools/fixtures/CRASH.ELF). Pure #![no_std] ring-3 graphical problem reporter and crash dump inspector shown automatically at boot or on-demand when a pending panic record is found on disk (/CRASHDMP.TXT and /CRASHDMP.DAT). Features: 1) Prominent Critical Alert banner card and window frame with problem diagnosis; 2) 4-tab interactive navigation across Overview (reason, exception vector, faulting EIP, CR2 fault address, error code, and failure assessment), CPU Registers (full 16-register CPU snapshot with EIP/CR2/INT_NO highlighting and EFLAGS decoding), Call Stack (EBP frame backtrace chain with symbolic module classifications across kernel init, paging, VFS, drivers, and userland), and Raw Report (scrollable monospace view of /CRASHDMP.TXT with line numbers); 3) Bottom action toolbar with [Dismiss], [Clear Record] driving SYS_CRASHDUMP_CTL (80) op 4, and [Reboot]; 4) Zero-syscall BufferSurface32 direct rasterization backed entirely by static BSS buffers within the 16KB userland stack budget; 5) Integrated boot notice and interactive commands ('crash', 'crash gui') in userland/shell/shell.c and userland/ring3-shell/shell.c. Verified via make crashrep-test (9 host tests) and automated QEMU boot test (270/270 assertions passing).</t>
   </si>
 </sst>
 </file>
@@ -1276,7 +1279,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1322,7 +1325,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.8461538461538461</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1343,7 +1346,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11">
@@ -1361,7 +1364,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="14">
@@ -1596,7 +1599,7 @@
       </c>
       <c r="B30" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 6 - First impressions",'Interface Track'!F2:F1000,"Done")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 6 - First impressions")</f>
@@ -1604,7 +1607,7 @@
       </c>
       <c r="D30" s="24">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -4802,10 +4805,12 @@
       <c r="E24" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="13"/>
+      <c r="F24" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="25" ht="60.0" customHeight="1">
       <c r="A25" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="231">
   <si>
     <t>Month</t>
   </si>
@@ -706,6 +706,12 @@
   </si>
   <si>
     <t>NovaOS Graphical Crash Reporter &amp; Diagnostic Inspector (userland/crashrep-rs/crashrep.rs, parser.rs, ffi.rs, build.sh, tools/fixtures/CRASHREP.ELF, tools/fixtures/CRASH.ELF). Pure #![no_std] ring-3 graphical problem reporter and crash dump inspector shown automatically at boot or on-demand when a pending panic record is found on disk (/CRASHDMP.TXT and /CRASHDMP.DAT). Features: 1) Prominent Critical Alert banner card and window frame with problem diagnosis; 2) 4-tab interactive navigation across Overview (reason, exception vector, faulting EIP, CR2 fault address, error code, and failure assessment), CPU Registers (full 16-register CPU snapshot with EIP/CR2/INT_NO highlighting and EFLAGS decoding), Call Stack (EBP frame backtrace chain with symbolic module classifications across kernel init, paging, VFS, drivers, and userland), and Raw Report (scrollable monospace view of /CRASHDMP.TXT with line numbers); 3) Bottom action toolbar with [Dismiss], [Clear Record] driving SYS_CRASHDUMP_CTL (80) op 4, and [Reboot]; 4) Zero-syscall BufferSurface32 direct rasterization backed entirely by static BSS buffers within the 16KB userland stack budget; 5) Integrated boot notice and interactive commands ('crash', 'crash gui') in userland/shell/shell.c and userland/ring3-shell/shell.c. Verified via make crashrep-test (9 host tests) and automated QEMU boot test (270/270 assertions passing).</t>
+  </si>
+  <si>
+    <t>NovaOS Graphical Software Updates Panel (userland/settings-rs/settings.rs, ffi.rs, build.sh, SETTINGS.ELF). Pure #![no_std] ring-3 administrative panel integrated into the Settings application (PanelKind::Updates) for atomic OS updates and dual boot-slot management. Interfaces with the kernel atomic update engine via SYS_OS_UPDATE (79) supporting NOVA_UPDATE_OP_STATUS, NOVA_UPDATE_OP_STAGE_AND_APPLY, NOVA_UPDATE_OP_CONFIRM, and NOVA_UPDATE_OP_ROLLBACK. Features: 1) Active boot slot telemetry banner displaying current partition (Slot A NOVAOS.BIN vs Slot B NOVAOS_B.BIN), health state (Normal, Testing with 3-attempt watchdog countdown, or Rolled Back), and fallback partition; 2) Dual-slot side-by-side architecture visualizer showing partition files, active/staging roles, and version records; 3) Full update workflow state machine (Idle -&gt; Checking -&gt; Available -&gt; ConfirmDialog -&gt; Applying -&gt; Complete) with 4-stage progress visualization (cryptographic HMAC-SHA256 signature verification, binary staging, write-ahead journal commit, and watchdog arming); 4) Interactive trial boot health controls ([Confirm System Healthy] and [Rollback to Previous Slot]) for test-mode verification; 5) Zero-syscall BufferSurface32 direct rasterization backed entirely by static BSS memory within the 16KB userland stack budget. Verified via make settings-test (24 host unit tests) and automated headless QEMU boot test.</t>
+  </si>
+  <si>
+    <t>NovaOS Graphical Software Updates Panel (userland/settings-rs/settings.rs, ffi.rs, build.sh, SETTINGS.ELF). Pure #![no_std] ring-3 administrative panel integrated into the Settings application (PanelKind::Updates) for atomic OS updates and dual boot-slot management. Interfaces with the kernel atomic update engine via SYS_OS_UPDATE (79) supporting NOVA_UPDATE_OP_STATUS, NOVA_UPDATE_OP_STAGE_AND_APPLY, NOVA_UPDATE_OP_CONFIRM, and NOVA_UPDATE_OP_ROLLBACK. Features: 1) Active boot slot telemetry banner displaying current partition (Slot A NOVAOS.BIN vs Slot B NOVAOS_B.BIN), health state (Normal, Testing with 3-attempt watchdog countdown, or Rolled Back), and fallback partition; 2) Dual-slot side-by-side architecture visualizer showing partition files, active/staging roles, and version records; 3) Full update workflow state machine (Idle -&gt; Checking -&gt; Available -&gt; ConfirmDialog -&gt; Applying -&gt; Complete) with 4-stage progress visualization (cryptographic HMAC-SHA256 signature verification, binary staging, write-ahead journal commit, and watchdog arming); 4) Interactive trial boot health controls ([Confirm System Healthy] and [Rollback to Previous Slot]) for test-mode verification; 5) Zero-syscall BufferSurface32 direct rasterization backed entirely by static BSS memory within the 16KB userland stack budget. Verified via make settings-test (24 host unit tests) and automated headless QEMU boot test.</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1285,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1325,7 +1331,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.8846153846153846</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1346,7 +1352,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -1364,7 +1370,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.875</v>
+        <v>0.8928571428571429</v>
       </c>
     </row>
     <row r="14">
@@ -1599,7 +1605,7 @@
       </c>
       <c r="B30" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 6 - First impressions",'Interface Track'!F2:F1000,"Done")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 6 - First impressions")</f>
@@ -1607,7 +1613,7 @@
       </c>
       <c r="D30" s="24">
         <f t="shared" si="3"/>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -4828,10 +4834,12 @@
       <c r="E25" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F25" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="13"/>
+      <c r="F25" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="26" ht="60.0" customHeight="1">
       <c r="A26" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="232">
   <si>
     <t>Month</t>
   </si>
@@ -712,6 +712,9 @@
   </si>
   <si>
     <t>NovaOS Graphical Software Updates Panel (userland/settings-rs/settings.rs, ffi.rs, build.sh, SETTINGS.ELF). Pure #![no_std] ring-3 administrative panel integrated into the Settings application (PanelKind::Updates) for atomic OS updates and dual boot-slot management. Interfaces with the kernel atomic update engine via SYS_OS_UPDATE (79) supporting NOVA_UPDATE_OP_STATUS, NOVA_UPDATE_OP_STAGE_AND_APPLY, NOVA_UPDATE_OP_CONFIRM, and NOVA_UPDATE_OP_ROLLBACK. Features: 1) Active boot slot telemetry banner displaying current partition (Slot A NOVAOS.BIN vs Slot B NOVAOS_B.BIN), health state (Normal, Testing with 3-attempt watchdog countdown, or Rolled Back), and fallback partition; 2) Dual-slot side-by-side architecture visualizer showing partition files, active/staging roles, and version records; 3) Full update workflow state machine (Idle -&gt; Checking -&gt; Available -&gt; ConfirmDialog -&gt; Applying -&gt; Complete) with 4-stage progress visualization (cryptographic HMAC-SHA256 signature verification, binary staging, write-ahead journal commit, and watchdog arming); 4) Interactive trial boot health controls ([Confirm System Healthy] and [Rollback to Previous Slot]) for test-mode verification; 5) Zero-syscall BufferSurface32 direct rasterization backed entirely by static BSS memory within the 16KB userland stack budget. Verified via make settings-test (24 host unit tests) and automated headless QEMU boot test.</t>
+  </si>
+  <si>
+    <t>NovaOS First-Run Setup Wizard (userland/firstrun-rs/firstrun.rs, crypto.rs, ffi.rs, build.sh, tools/fixtures/FIRSTRUN.ELF, tools/fixtures/SETUP.ELF). Pure #![no_std] ring-3 graphical first-run setup wizard extending the original firstrun.c architecture into a modern multi-step guided setup flow. Features: 1) Hardware telemetry &amp; welcome view (CPU vendor/model/cores, RAM capacity, detected storage media, network adapters); 2) Machine identity configuration (hostname validation, init executable selection, SYSTEM.CFG serialization with 'NVCF' magic); 3) Primary administrator account setup (UID 0 / GID 0, real RFC 8018 PBKDF2-HMAC-SHA256 hashing with 4096 iterations, cryptographic salt derivation, USERS.CFG serialization with 'NVUS' magic); 4) Network configuration (DHCP vs static IPv4 address/gateway/DNS, stateful firewall policy generation, FIREWALL.CFG serialization); 5) Visual preferences &amp; accessibility (Theme selection [Dark, Light, HighContrast], font scaling [100%, 125%, 150%, 200%], cursor themes [White, Amber, Retro], ACCESS.CFG persistence with CRC checksum); 6) Review &amp; deployment summary with progressive atomic writing of all configuration files; 7) Setup completion view offering direct launch of the Graphical Desktop (WM.ELF) or Developer Shell (SHELL.ELF); 8) Zero-syscall BufferSurface32 rasterization adhering to the 16KB userland stack budget by utilizing static BSS memory. Verified via make firstrun-test (8 host unit tests) and automated QEMU boot test.</t>
   </si>
 </sst>
 </file>
@@ -1285,7 +1288,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1331,7 +1334,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.9230769230769231</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1352,7 +1355,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
@@ -1370,7 +1373,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.8928571428571429</v>
+        <v>0.9107142857142857</v>
       </c>
     </row>
     <row r="14">
@@ -1605,7 +1608,7 @@
       </c>
       <c r="B30" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 6 - First impressions",'Interface Track'!F2:F1000,"Done")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 6 - First impressions")</f>
@@ -1613,7 +1616,7 @@
       </c>
       <c r="D30" s="24">
         <f t="shared" si="3"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -4857,10 +4860,12 @@
       <c r="E26" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F26" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="13"/>
+      <c r="F26" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="27" ht="60.0" customHeight="1">
       <c r="A27" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="233">
   <si>
     <t>Month</t>
   </si>
@@ -715,6 +715,9 @@
   </si>
   <si>
     <t>NovaOS First-Run Setup Wizard (userland/firstrun-rs/firstrun.rs, crypto.rs, ffi.rs, build.sh, tools/fixtures/FIRSTRUN.ELF, tools/fixtures/SETUP.ELF). Pure #![no_std] ring-3 graphical first-run setup wizard extending the original firstrun.c architecture into a modern multi-step guided setup flow. Features: 1) Hardware telemetry &amp; welcome view (CPU vendor/model/cores, RAM capacity, detected storage media, network adapters); 2) Machine identity configuration (hostname validation, init executable selection, SYSTEM.CFG serialization with 'NVCF' magic); 3) Primary administrator account setup (UID 0 / GID 0, real RFC 8018 PBKDF2-HMAC-SHA256 hashing with 4096 iterations, cryptographic salt derivation, USERS.CFG serialization with 'NVUS' magic); 4) Network configuration (DHCP vs static IPv4 address/gateway/DNS, stateful firewall policy generation, FIREWALL.CFG serialization); 5) Visual preferences &amp; accessibility (Theme selection [Dark, Light, HighContrast], font scaling [100%, 125%, 150%, 200%], cursor themes [White, Amber, Retro], ACCESS.CFG persistence with CRC checksum); 6) Review &amp; deployment summary with progressive atomic writing of all configuration files; 7) Setup completion view offering direct launch of the Graphical Desktop (WM.ELF) or Developer Shell (SHELL.ELF); 8) Zero-syscall BufferSurface32 rasterization adhering to the 16KB userland stack budget by utilizing static BSS memory. Verified via make firstrun-test (8 host unit tests) and automated QEMU boot test.</t>
+  </si>
+  <si>
+    <t>NovaOS Full UI QA Pass &amp; End-User Documentation (tools/tests/run_ui_qa_pass.sh, make ui-qa, docs/USER_GUIDE.md, RozeHub Documentation Database &amp; Local Server). Completed comprehensive QA testing pass verifying all 13 ring-3 applications and graphical subsystems developed across Months 1-6: 1) Shared UI Design System (userland/ui-rs - 23 host unit tests); 2) Window Manager &amp; Compositor with 8-zone snapping and tiling (userland/wm-rs - 17 host tests); 3) File Manager (userland/files-rs - 4 host tests); 4) In-Window Terminal Emulator (userland/term-rs - 5 host tests); 5) Monospace Text Editor (userland/edit-rs - 5 host tests); 6) Software Store &amp; Package Manager (userland/store-rs - 6 host tests); 7) Settings Shell &amp; Admin Panels (userland/settings-rs - 24 host tests); 8) Graphical Login &amp; Session Manager (userland/login-rs - 6 host tests); 9) Structured Kernel Log Viewer (userland/klog-rs - 12 host tests); 10) Activity Monitor &amp; Resource Meters (userland/actmon-rs - 10 host tests); 11) Graphical Installer Wizard (userland/installer-rs - 10 host tests); 12) Graphical Crash Reporter (userland/crashrep-rs - 9 host tests); 13) First-Run Setup Wizard (userland/firstrun-rs - 10 host tests). Total: 141 UI unit tests passing across all 13 modules with 100% pass rate. Authored complete, authoritative 8-chapter End-User Manual (docs/USER_GUIDE.md) and seeded comprehensive production documentation into RozeHub with 8 sections and 21 pages, running live on http://127.0.0.1:8000/docs/novaos. Verified via make ui-qa and automated QEMU boot test (275/275 assertions passing).</t>
   </si>
 </sst>
 </file>
@@ -1288,7 +1291,7 @@
       </c>
       <c r="D5" s="17">
         <f>COUNTIF('Interface Track'!F2:F27,"Done")</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>27</v>
@@ -1334,7 +1337,7 @@
       </c>
       <c r="D7" s="19">
         <f>D5/D6</f>
-        <v>0.9615384615384616</v>
+        <v>1.0</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>186</v>
@@ -1355,7 +1358,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -1373,7 +1376,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.9107142857142857</v>
+        <v>0.9285714285714286</v>
       </c>
     </row>
     <row r="14">
@@ -1608,7 +1611,7 @@
       </c>
       <c r="B30" s="17">
         <f>COUNTIFS('Interface Track'!A2:A1000,"Month 6 - First impressions",'Interface Track'!F2:F1000,"Done")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" s="17">
         <f>COUNTIF('Interface Track'!A2:A1000,"Month 6 - First impressions")</f>
@@ -1616,7 +1619,7 @@
       </c>
       <c r="D30" s="24">
         <f t="shared" si="3"/>
-        <v>0.8</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -4883,10 +4886,12 @@
       <c r="E27" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F27" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="13"/>
+      <c r="F27" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="28" ht="15.75" customHeight="1"/>
     <row r="29" ht="15.75" customHeight="1"/>

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="234">
   <si>
     <t>Month</t>
   </si>
@@ -718,6 +718,9 @@
   </si>
   <si>
     <t>NovaOS Full UI QA Pass &amp; End-User Documentation (tools/tests/run_ui_qa_pass.sh, make ui-qa, docs/USER_GUIDE.md, RozeHub Documentation Database &amp; Local Server). Completed comprehensive QA testing pass verifying all 13 ring-3 applications and graphical subsystems developed across Months 1-6: 1) Shared UI Design System (userland/ui-rs - 23 host unit tests); 2) Window Manager &amp; Compositor with 8-zone snapping and tiling (userland/wm-rs - 17 host tests); 3) File Manager (userland/files-rs - 4 host tests); 4) In-Window Terminal Emulator (userland/term-rs - 5 host tests); 5) Monospace Text Editor (userland/edit-rs - 5 host tests); 6) Software Store &amp; Package Manager (userland/store-rs - 6 host tests); 7) Settings Shell &amp; Admin Panels (userland/settings-rs - 24 host tests); 8) Graphical Login &amp; Session Manager (userland/login-rs - 6 host tests); 9) Structured Kernel Log Viewer (userland/klog-rs - 12 host tests); 10) Activity Monitor &amp; Resource Meters (userland/actmon-rs - 10 host tests); 11) Graphical Installer Wizard (userland/installer-rs - 10 host tests); 12) Graphical Crash Reporter (userland/crashrep-rs - 9 host tests); 13) First-Run Setup Wizard (userland/firstrun-rs - 10 host tests). Total: 141 UI unit tests passing across all 13 modules with 100% pass rate. Authored complete, authoritative 8-chapter End-User Manual (docs/USER_GUIDE.md) and seeded comprehensive production documentation into RozeHub with 8 sections and 21 pages, running live on http://127.0.0.1:8000/docs/novaos. Verified via make ui-qa and automated QEMU boot test (275/275 assertions passing).</t>
+  </si>
+  <si>
+    <t>Comprehensive Automated Boot-Time Test Suite Expansion (tools/python/test_runner.py, test: target in Makefile). Maintained and extended NovaOS's strict 'verify, don't assume' discipline by expanding the structured Python test runner to cover every single feature across both Kernel and Interface tracks as they landed. Added 42 new granular assertions across core hardware, kernel subsystems, and all 13 ring-3 applications, scaling the suite from 275 to 317 total automated assertions with 100% pass rate: 1) Kernel foundation &amp; hardware: interrupt gate 0x80 installation with DPL 3, 8254 PIT timer 100 Hz calibration, PS/2 mouse IRQ12 packet streaming, ATA LBA28 PIO detection, ACPI MADT 2-core SMP verification, ACPI S5 shutdown control block discovery, in-kernel DNS UDP resolution, FAT32 write-ahead journal clean recovery, journal self-test atomicity/replay, and crash dump auto-export; 2) Month 3 Core apps: File Manager (files_metadata, files_hit_testing, files_preview, files_move_delete, files_rendering), Terminal (term_grid, term_wrap, term_ansi, term_history, term_dispatch, term_rendering), Text Editor (edit_buffer, edit_backspace, edit_vfs_io, edit_font_modes, edit_mouse_toolbar, edit_rendering), Package Store (store_manifest, store_crypto, store_db_state, store_search, store_telemetry, store_rendering), and Login Screen (login_bad_password, login_uid_transition, login_admin_auth, login_masking, login_rendering); 3) Month 6 First impressions: First-Run Setup Wizard (firstrun_identity, firstrun_account_synthesis, firstrun_cfg_generation). Automated headless QEMU boot test completes in ~91 seconds, verifying all 317 assertions with 0 failures and 0 panics.</t>
   </si>
 </sst>
 </file>
@@ -1298,7 +1301,7 @@
       </c>
       <c r="F5" s="17">
         <f>COUNTIF(Release!F2:F5,"Done")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1344,7 +1347,7 @@
       </c>
       <c r="F7" s="20">
         <f>F5/F6</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9">
@@ -1358,7 +1361,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
@@ -1376,7 +1379,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.9285714285714286</v>
+        <v>0.9464285714285714</v>
       </c>
     </row>
     <row r="14">
@@ -5890,7 +5893,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -5945,10 +5948,12 @@
       <c r="E2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="13"/>
+      <c r="F2" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="3" ht="60.0" customHeight="1">
       <c r="A3" s="5" t="s">
@@ -7012,6 +7017,6 @@
   <printOptions/>
   <pageMargins bottom="0.5" footer="0.0" header="0.0" left="0.35" right="0.35" top="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <drawing ns1:id="rId1"/>
 </worksheet>
 </file>
--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
   <si>
     <t>Month</t>
   </si>
@@ -721,6 +721,9 @@
   </si>
   <si>
     <t>Comprehensive Automated Boot-Time Test Suite Expansion (tools/python/test_runner.py, test: target in Makefile). Maintained and extended NovaOS's strict 'verify, don't assume' discipline by expanding the structured Python test runner to cover every single feature across both Kernel and Interface tracks as they landed. Added 42 new granular assertions across core hardware, kernel subsystems, and all 13 ring-3 applications, scaling the suite from 275 to 317 total automated assertions with 100% pass rate: 1) Kernel foundation &amp; hardware: interrupt gate 0x80 installation with DPL 3, 8254 PIT timer 100 Hz calibration, PS/2 mouse IRQ12 packet streaming, ATA LBA28 PIO detection, ACPI MADT 2-core SMP verification, ACPI S5 shutdown control block discovery, in-kernel DNS UDP resolution, FAT32 write-ahead journal clean recovery, journal self-test atomicity/replay, and crash dump auto-export; 2) Month 3 Core apps: File Manager (files_metadata, files_hit_testing, files_preview, files_move_delete, files_rendering), Terminal (term_grid, term_wrap, term_ansi, term_history, term_dispatch, term_rendering), Text Editor (edit_buffer, edit_backspace, edit_vfs_io, edit_font_modes, edit_mouse_toolbar, edit_rendering), Package Store (store_manifest, store_crypto, store_db_state, store_search, store_telemetry, store_rendering), and Login Screen (login_bad_password, login_uid_transition, login_admin_auth, login_masking, login_rendering); 3) Month 6 First impressions: First-Run Setup Wizard (firstrun_identity, firstrun_account_synthesis, firstrun_cfg_generation). Automated headless QEMU boot test completes in ~91 seconds, verifying all 317 assertions with 0 failures and 0 panics.</t>
+  </si>
+  <si>
+    <t>Desktop &amp; Server Editions Split Architecture from Shared Kernel (tools/build-disk-image.sh, Makefile, tools/tests/run_editions_test.sh, userland/shell/firstrun.c, kernel/task/exec_trust_demo.c, kernel/task/sandbox_demo.c, tools/python/test_runner.py). Implemented dual-install profile architecture (Desktop vs Server) from a 100% shared kernel binary (novaos.bin / novaos.iso): 1) Build-time profile engine (tools/build-disk-image.sh): supports --profile=desktop|server, positional profile arguments, and PROFILE environment variables. In desktop profile (disk.img), installs full graphical desktop suite (WM.ELF, GUI.ELF, FILES.ELF, SETTINGS.ELF, TERM.ELF, EDIT.ELF, STORE.ELF, LOGIN.ELF, INSTALL.ELF, CRASHREP.ELF, CRASH.ELF, FIRSTRUN.ELF, SETUP.ELF, ACCESS.CFG, EDITOR.PKG, GAME.PKG) and provisions /EDITION.TXT as 'NovaOS Desktop Edition (x86_32)'. In server profile (disk-server.img), strips ~6.7MB of compositor/GUI apps and desktop packages, installs headless MOTD banner (/MOTD.TXT), provisions /EDITION.TXT as 'NovaOS Server Edition (x86_32 headless)', generates server-tailored SYSTEM.CFG (81 bytes: NVCF, hostname 'novaos-server', root user 'admin', init 'NOVAINIT.ELF'), and provisions server packet filter /FIREWALL.CFG and supervisor /SERVICES.CFG while retaining core CLI tools and services (SHELL.ELF, NOVAINIT.ELF, CAT.ELF, LS.ELF, ECHO.ELF, CP.ELF, RM.ELF, SYSINFO.ELF, PING.ELF, UPDATE.ELF, KLOG.ELF, ACTMON.ELF, TPROBE.ELF, and test harnesses); 2) Kernel &amp; Ring-3 Edition Adaptation: userland/shell/firstrun.c detects /EDITION.TXT at boot and logs system edition; kernel/task/exec_trust_demo.c and kernel/task/sandbox_demo.c adapt ring-3 app selftests to edition identity, skipping GUI apps on server profile while running headless system tools (KLOG.ELF, ACTMON.ELF, MACTEST.ELF) and logging '[sandbox] PASS: Server edition profile active'; 3) Makefile &amp; Build Targets: added PROFILE ?= desktop, disk-desktop, disk-server, server-image, run-server, test-server, and test-editions targets; 4) Verification &amp; Automated Test Suite: created tools/tests/run_editions_test.sh (100% pass across 46 validation checks); extended tools/python/test_runner.py with --profile support, edition_desktop_detected (318/318 passed in 105s), and edition_server_detected / server_edition_profile_verified (247/247 passed in 87s).</t>
   </si>
 </sst>
 </file>
@@ -1301,7 +1304,7 @@
       </c>
       <c r="F5" s="17">
         <f>COUNTIF(Release!F2:F5,"Done")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1347,7 +1350,7 @@
       </c>
       <c r="F7" s="20">
         <f>F5/F6</f>
-        <v>0.25</v>
+        <v>0.50</v>
       </c>
     </row>
     <row r="9">
@@ -1361,7 +1364,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -1379,7 +1382,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.9464285714285714</v>
+        <v>0.9642857142857143</v>
       </c>
     </row>
     <row r="14">
@@ -5971,10 +5974,12 @@
       <c r="E3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="13"/>
+      <c r="F3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="4" ht="60.0" customHeight="1">
       <c r="A4" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="237">
   <si>
     <t>Month</t>
   </si>
@@ -724,6 +724,12 @@
   </si>
   <si>
     <t>Desktop &amp; Server Editions Split Architecture from Shared Kernel (tools/build-disk-image.sh, Makefile, tools/tests/run_editions_test.sh, userland/shell/firstrun.c, kernel/task/exec_trust_demo.c, kernel/task/sandbox_demo.c, tools/python/test_runner.py). Implemented dual-install profile architecture (Desktop vs Server) from a 100% shared kernel binary (novaos.bin / novaos.iso): 1) Build-time profile engine (tools/build-disk-image.sh): supports --profile=desktop|server, positional profile arguments, and PROFILE environment variables. In desktop profile (disk.img), installs full graphical desktop suite (WM.ELF, GUI.ELF, FILES.ELF, SETTINGS.ELF, TERM.ELF, EDIT.ELF, STORE.ELF, LOGIN.ELF, INSTALL.ELF, CRASHREP.ELF, CRASH.ELF, FIRSTRUN.ELF, SETUP.ELF, ACCESS.CFG, EDITOR.PKG, GAME.PKG) and provisions /EDITION.TXT as 'NovaOS Desktop Edition (x86_32)'. In server profile (disk-server.img), strips ~6.7MB of compositor/GUI apps and desktop packages, installs headless MOTD banner (/MOTD.TXT), provisions /EDITION.TXT as 'NovaOS Server Edition (x86_32 headless)', generates server-tailored SYSTEM.CFG (81 bytes: NVCF, hostname 'novaos-server', root user 'admin', init 'NOVAINIT.ELF'), and provisions server packet filter /FIREWALL.CFG and supervisor /SERVICES.CFG while retaining core CLI tools and services (SHELL.ELF, NOVAINIT.ELF, CAT.ELF, LS.ELF, ECHO.ELF, CP.ELF, RM.ELF, SYSINFO.ELF, PING.ELF, UPDATE.ELF, KLOG.ELF, ACTMON.ELF, TPROBE.ELF, and test harnesses); 2) Kernel &amp; Ring-3 Edition Adaptation: userland/shell/firstrun.c detects /EDITION.TXT at boot and logs system edition; kernel/task/exec_trust_demo.c and kernel/task/sandbox_demo.c adapt ring-3 app selftests to edition identity, skipping GUI apps on server profile while running headless system tools (KLOG.ELF, ACTMON.ELF, MACTEST.ELF) and logging '[sandbox] PASS: Server edition profile active'; 3) Makefile &amp; Build Targets: added PROFILE ?= desktop, disk-desktop, disk-server, server-image, run-server, test-server, and test-editions targets; 4) Verification &amp; Automated Test Suite: created tools/tests/run_editions_test.sh (100% pass across 46 validation checks); extended tools/python/test_runner.py with --profile support, edition_desktop_detected (318/318 passed in 105s), and edition_server_detected / server_edition_profile_verified (247/247 passed in 87s).</t>
+  </si>
+  <si>
+    <t>C, Rust, Python &amp; Shell</t>
+  </si>
+  <si>
+    <t>Security Review &amp; Cross-Track Permission Boundary Audit (docs/SECURITY_REVIEW.md, kernel/security/security_audit.c, kernel/security/security_audit.h, tools/tests/run_security_audit_test.sh, Makefile). Completed comprehensive, cross-track security and permission audit across all 6 months of development: 1) Syscall authorization matrix &amp; bounds validation across all 84 system calls, enforcing high-memory kernel isolation (0xC0000000 virtual split, Page 0 IVT rejection, integer overflow/wraparound prevention via paging_user_range_ok), capability allowlists (allowed_files, allowed_hosts, can_spawn, can_open_any_file), MAC profile enforcement, and root privilege gates on mutating syscalls (SYS_OS_UPDATE, SYS_CRASHDUMP_CTL, SYS_DISK_INSTALL, SYS_FW_CTL, SYS_SHUTDOWN); 2) Least-privilege matrix across all 13 ring-3 applications (NOVAINIT.ELF, LOGIN.ELF, FIRSTRUN.ELF, SHELL.ELF, WM.ELF, FILES.ELF, SETTINGS.ELF, TERM.ELF, EDIT.ELF, STORE.ELF, KLOG.ELF, ACTMON.ELF, INSTALL.ELF, CRASHREP.ELF), verifying strict UID/GID privilege dropping, sandboxed capability confinement, and mandatory memory zeroization of plaintext password buffers in LOGIN.ELF (login.rs), FIRSTRUN.ELF (firstrun.rs), and firstrun.c; 3) Framebuffer single-owner mutual exclusion (SYS_FB_ACQUIRE/RELEASE returning -EBUSY on collision), IPC messaging sender PID/UID kernel-stamped immutability, and shared memory ACLs (SYS_SHM_GRANT); 4) Expanded in-kernel boot self-test (Phase 98, Section 5: '[ OK ] audit: cross-track application least-privilege matrix verified') and created dedicated host validation script tools/tests/run_security_audit_test.sh (make test-security) passing 10/10 checks; 5) Seeded technical documentation in RozeHub (http://127.0.0.1:8000/docs/novaos). Validated with 100% pass rate: Desktop Edition (319/319 assertions), Server Edition (248/248 assertions).</t>
   </si>
 </sst>
 </file>
@@ -1304,7 +1310,7 @@
       </c>
       <c r="F5" s="17">
         <f>COUNTIF(Release!F2:F5,"Done")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1350,7 +1356,7 @@
       </c>
       <c r="F7" s="20">
         <f>F5/F6</f>
-        <v>0.50</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="9">
@@ -1364,7 +1370,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
@@ -1382,7 +1388,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.9642857142857143</v>
+        <v>0.9821428571428571</v>
       </c>
     </row>
     <row r="14">
@@ -5995,12 +6001,14 @@
         <v>54</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="13"/>
+        <v>235</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="5" ht="60.0" customHeight="1">
       <c r="A5" s="5" t="s">

--- a/NovaOS_Build_Plan.xlsx
+++ b/NovaOS_Build_Plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="239">
   <si>
     <t>Month</t>
   </si>
@@ -730,6 +730,12 @@
   </si>
   <si>
     <t>Security Review &amp; Cross-Track Permission Boundary Audit (docs/SECURITY_REVIEW.md, kernel/security/security_audit.c, kernel/security/security_audit.h, tools/tests/run_security_audit_test.sh, Makefile). Completed comprehensive, cross-track security and permission audit across all 6 months of development: 1) Syscall authorization matrix &amp; bounds validation across all 84 system calls, enforcing high-memory kernel isolation (0xC0000000 virtual split, Page 0 IVT rejection, integer overflow/wraparound prevention via paging_user_range_ok), capability allowlists (allowed_files, allowed_hosts, can_spawn, can_open_any_file), MAC profile enforcement, and root privilege gates on mutating syscalls (SYS_OS_UPDATE, SYS_CRASHDUMP_CTL, SYS_DISK_INSTALL, SYS_FW_CTL, SYS_SHUTDOWN); 2) Least-privilege matrix across all 13 ring-3 applications (NOVAINIT.ELF, LOGIN.ELF, FIRSTRUN.ELF, SHELL.ELF, WM.ELF, FILES.ELF, SETTINGS.ELF, TERM.ELF, EDIT.ELF, STORE.ELF, KLOG.ELF, ACTMON.ELF, INSTALL.ELF, CRASHREP.ELF), verifying strict UID/GID privilege dropping, sandboxed capability confinement, and mandatory memory zeroization of plaintext password buffers in LOGIN.ELF (login.rs), FIRSTRUN.ELF (firstrun.rs), and firstrun.c; 3) Framebuffer single-owner mutual exclusion (SYS_FB_ACQUIRE/RELEASE returning -EBUSY on collision), IPC messaging sender PID/UID kernel-stamped immutability, and shared memory ACLs (SYS_SHM_GRANT); 4) Expanded in-kernel boot self-test (Phase 98, Section 5: '[ OK ] audit: cross-track application least-privilege matrix verified') and created dedicated host validation script tools/tests/run_security_audit_test.sh (make test-security) passing 10/10 checks; 5) Seeded technical documentation in RozeHub (http://127.0.0.1:8000/docs/novaos). Validated with 100% pass rate: Desktop Edition (319/319 assertions), Server Edition (248/248 assertions).</t>
+  </si>
+  <si>
+    <t>Shell, Python &amp; C</t>
+  </si>
+  <si>
+    <t>v1.0 Release Candidate Build &amp; Final Sign-Off Certification (docs/RELEASE_SIGNOFF_V1.0.md, release/v1.0.0/, tools/release/release_signoff.sh, Makefile). Final build-and-sign-off milestone successfully achieved - 100% of 6-Month Build Plan delivered across all tracks (56/56 tasks): 1) Release Binaries &amp; Packaging: generated production-ready release images in release/v1.0.0/: novaos.iso (3.8MB hybrid bootable ISO image: El Torito CD-ROM + BIOS/USB MBR disk), novaos-desktop.img (102MB partitioned desktop image with full 13-app GUI suite), novaos-server.img (102MB partitioned headless server image), and novaos.bin (438KB shared kernel binary); 2) Cryptographic Integrity Verification: generated and verified SHA-256 cryptographic digests (SHA256SUMS and individual .sha256 digests); 3) Automated Release Qualification Suite: author tools/release/release_signoff.sh and Makefile 'release' / 'release-check' targets executing 9 comprehensive qualification phases; 4) Documentation &amp; Changelog: authored official release qualification report docs/RELEASE_SIGNOFF_V1.0.md, updated CHANGELOG.md with full 56-feature milestone history, and updated README.md; 5) RozeHub Release Publishing: seeded v1.0.0 release notes and verification checklist in RozeHub documentation (http://127.0.0.1:8000/docs/novaos). Validated with 100% test pass rate across all suites: Desktop Edition (319/319 assertions), Server Edition (248/248 assertions), Security Audit (10/10 checks), Editions Validation (46/46 checks), and UI QA Pass (13/13 suites). Certified production ready.</t>
   </si>
 </sst>
 </file>
@@ -1310,7 +1316,7 @@
       </c>
       <c r="F5" s="17">
         <f>COUNTIF(Release!F2:F5,"Done")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1356,7 +1362,7 @@
       </c>
       <c r="F7" s="20">
         <f>F5/F6</f>
-        <v>0.75</v>
+        <v>1.00</v>
       </c>
     </row>
     <row r="9">
@@ -1370,7 +1376,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B11" si="1">B5+D5+F5</f>
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -1388,7 +1394,7 @@
       </c>
       <c r="B12" s="22">
         <f>B10/B11</f>
-        <v>0.9821428571428571</v>
+        <v>1.00</v>
       </c>
     </row>
     <row r="14">
@@ -6024,12 +6030,14 @@
         <v>62</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="13"/>
+        <v>237</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
